--- a/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/operational_risks.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/operational_risks.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Continuity</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Key person</t>
+          <t>Continuity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -541,12 +541,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Process failure</t>
+          <t>Continuity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Continuity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -575,12 +575,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Process failure</t>
+          <t>Continuity</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>Continuity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Continuity</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -626,12 +626,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Continuity</t>
+          <t>Key person</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -694,12 +694,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>Process failure</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Supplier</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Key person</t>
+          <t>Continuity</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Process failure</t>
+          <t>Key person</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Continuity</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Supplier</t>
+          <t>Process failure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
